--- a/Data/Export/Common/ItemType_道具类型.xlsx
+++ b/Data/Export/Common/ItemType_道具类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7059D9-89A7-41AF-8970-0DC71F319B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF840FB2-2752-454E-A962-DDA8EF4B7B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemTypes" sheetId="36" r:id="rId1"/>
@@ -1819,7 +1819,7 @@
         <v>49</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>

--- a/Data/Export/Common/ItemType_道具类型.xlsx
+++ b/Data/Export/Common/ItemType_道具类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF840FB2-2752-454E-A962-DDA8EF4B7B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E2F34A-A120-4177-8AA3-9E21539FB19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9540" yWindow="1350" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemTypes" sheetId="36" r:id="rId1"/>
@@ -1554,7 +1554,7 @@
         <v>58</v>
       </c>
       <c r="I11" s="4">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>34</v>
@@ -1657,7 +1657,7 @@
         <v>58</v>
       </c>
       <c r="I13" s="4">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>33</v>
@@ -1804,7 +1804,7 @@
         <v>58</v>
       </c>
       <c r="I16" s="4">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>37</v>

--- a/Data/Export/Common/ItemType_道具类型.xlsx
+++ b/Data/Export/Common/ItemType_道具类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E2F34A-A120-4177-8AA3-9E21539FB19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B725F0D2-B58A-4692-B366-4EB4AB2B7847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9540" yWindow="1350" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemTypes" sheetId="36" r:id="rId1"/>
@@ -1355,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="4">
         <v>3</v>
@@ -1401,7 +1401,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4">
         <v>4</v>
@@ -1447,7 +1447,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="4">
         <v>5</v>
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" s="4">
         <v>6</v>
@@ -1545,7 +1545,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4">
         <v>6</v>
@@ -1596,7 +1596,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4">
         <v>7</v>
@@ -1699,7 +1699,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4">
         <v>8</v>
@@ -1743,7 +1743,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F15" s="4">
         <v>8</v>
@@ -1795,7 +1795,7 @@
         <v>4</v>
       </c>
       <c r="E16" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16" s="4">
         <v>8</v>
@@ -1846,7 +1846,7 @@
         <v>127</v>
       </c>
       <c r="E17" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F17" s="4">
         <v>13</v>
@@ -1890,7 +1890,7 @@
         <v>127</v>
       </c>
       <c r="E18" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F18" s="4">
         <v>14</v>
@@ -1926,7 +1926,7 @@
         <v>127</v>
       </c>
       <c r="E19" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4">
         <v>15</v>
@@ -1953,7 +1953,7 @@
         <v>127</v>
       </c>
       <c r="E20" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F20" s="4">
         <v>16</v>
@@ -2007,7 +2007,7 @@
         <v>127</v>
       </c>
       <c r="E22" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F22" s="4">
         <v>18</v>
@@ -2034,7 +2034,7 @@
         <v>127</v>
       </c>
       <c r="E23" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F23" s="4">
         <v>19</v>
@@ -2061,7 +2061,7 @@
         <v>127</v>
       </c>
       <c r="E24" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F24" s="4">
         <v>20</v>
@@ -2088,7 +2088,7 @@
         <v>127</v>
       </c>
       <c r="E25" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F25" s="4">
         <v>21</v>
@@ -2115,7 +2115,7 @@
         <v>127</v>
       </c>
       <c r="E26" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F26" s="4">
         <v>22</v>
@@ -2142,7 +2142,7 @@
         <v>127</v>
       </c>
       <c r="E27" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F27" s="4">
         <v>23</v>
@@ -2169,7 +2169,7 @@
         <v>127</v>
       </c>
       <c r="E28" s="4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F28" s="4">
         <v>24</v>
@@ -2196,7 +2196,7 @@
         <v>5</v>
       </c>
       <c r="E29" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="4">
         <v>25</v>
@@ -2223,7 +2223,7 @@
         <v>5</v>
       </c>
       <c r="E30" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="4">
         <v>26</v>
@@ -2250,7 +2250,7 @@
         <v>5</v>
       </c>
       <c r="E31" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="4">
         <v>27</v>
@@ -2277,7 +2277,7 @@
         <v>5</v>
       </c>
       <c r="E32" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="4">
         <v>28</v>
@@ -2304,7 +2304,7 @@
         <v>5</v>
       </c>
       <c r="E33" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="4">
         <v>29</v>
@@ -2331,7 +2331,7 @@
         <v>5</v>
       </c>
       <c r="E34" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="4">
         <v>30</v>
@@ -2358,7 +2358,7 @@
         <v>5</v>
       </c>
       <c r="E35" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="4">
         <v>31</v>
@@ -2385,7 +2385,7 @@
         <v>5</v>
       </c>
       <c r="E36" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="4">
         <v>32</v>
@@ -2412,7 +2412,7 @@
         <v>5</v>
       </c>
       <c r="E37" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="4">
         <v>33</v>
@@ -2439,7 +2439,7 @@
         <v>5</v>
       </c>
       <c r="E38" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="4">
         <v>34</v>
@@ -2466,7 +2466,7 @@
         <v>5</v>
       </c>
       <c r="E39" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="4">
         <v>35</v>
@@ -2574,7 +2574,7 @@
         <v>5</v>
       </c>
       <c r="E43" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43" s="4">
         <v>39</v>
@@ -2601,7 +2601,7 @@
         <v>5</v>
       </c>
       <c r="E44" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44" s="4">
         <v>40</v>
@@ -2628,7 +2628,7 @@
         <v>5</v>
       </c>
       <c r="E45" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45" s="4">
         <v>41</v>
@@ -2655,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="E46" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" s="4">
         <v>42</v>
@@ -2681,7 +2681,7 @@
         <v>5</v>
       </c>
       <c r="E47" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47" s="4">
         <v>43</v>
@@ -2704,7 +2704,7 @@
         <v>5</v>
       </c>
       <c r="E48" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" s="4">
         <v>44</v>
@@ -2727,7 +2727,7 @@
         <v>5</v>
       </c>
       <c r="E49" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49" s="4">
         <v>45</v>
@@ -2750,7 +2750,7 @@
         <v>5</v>
       </c>
       <c r="E50" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F50" s="4">
         <v>46</v>
@@ -2773,7 +2773,7 @@
         <v>5</v>
       </c>
       <c r="E51" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" s="4">
         <v>47</v>
@@ -2796,7 +2796,7 @@
         <v>5</v>
       </c>
       <c r="E52" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F52" s="4">
         <v>48</v>
@@ -2819,7 +2819,7 @@
         <v>5</v>
       </c>
       <c r="E53" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F53" s="4">
         <v>49</v>
@@ -2842,7 +2842,7 @@
         <v>5</v>
       </c>
       <c r="E54" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F54" s="4">
         <v>50</v>
@@ -2865,7 +2865,7 @@
         <v>5</v>
       </c>
       <c r="E55" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F55" s="4">
         <v>51</v>
@@ -2888,7 +2888,7 @@
         <v>5</v>
       </c>
       <c r="E56" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F56" s="4">
         <v>52</v>
@@ -2911,7 +2911,7 @@
         <v>5</v>
       </c>
       <c r="E57" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F57" s="4">
         <v>53</v>
@@ -2934,7 +2934,7 @@
         <v>5</v>
       </c>
       <c r="E58" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F58" s="4">
         <v>54</v>
@@ -2957,7 +2957,7 @@
         <v>5</v>
       </c>
       <c r="E59" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F59" s="4">
         <v>55</v>
@@ -2980,7 +2980,7 @@
         <v>5</v>
       </c>
       <c r="E60" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F60" s="4">
         <v>56</v>
@@ -3003,7 +3003,7 @@
         <v>5</v>
       </c>
       <c r="E61" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F61" s="4">
         <v>57</v>
@@ -3026,7 +3026,7 @@
         <v>5</v>
       </c>
       <c r="E62" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F62" s="4">
         <v>58</v>
@@ -3049,7 +3049,7 @@
         <v>5</v>
       </c>
       <c r="E63" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F63" s="4">
         <v>59</v>
@@ -3072,7 +3072,7 @@
         <v>5</v>
       </c>
       <c r="E64" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F64" s="4">
         <v>60</v>
@@ -3095,7 +3095,7 @@
         <v>5</v>
       </c>
       <c r="E65" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F65" s="4">
         <v>61</v>
@@ -3118,7 +3118,7 @@
         <v>5</v>
       </c>
       <c r="E66" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F66" s="4">
         <v>62</v>
@@ -3141,7 +3141,7 @@
         <v>5</v>
       </c>
       <c r="E67" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F67" s="4">
         <v>63</v>
@@ -3164,7 +3164,7 @@
         <v>5</v>
       </c>
       <c r="E68" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F68" s="4">
         <v>64</v>
@@ -3187,7 +3187,7 @@
         <v>5</v>
       </c>
       <c r="E69" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F69" s="4">
         <v>65</v>
@@ -3208,7 +3208,7 @@
         <v>5</v>
       </c>
       <c r="E70" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F70" s="4">
         <v>66</v>
@@ -3228,7 +3228,7 @@
         <v>5</v>
       </c>
       <c r="E71" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F71" s="4">
         <v>67</v>
